--- a/data/dividends_info_20260910.xlsx
+++ b/data/dividends_info_20260910.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44.375</v>
+        <v>43.63999938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2028169014084507</v>
+        <v>0.2062328168165564</v>
       </c>
       <c r="J2" t="n">
         <v>186</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.84999847412109</v>
+        <v>65.59999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.063022044374228</v>
+        <v>1.067073195552202</v>
       </c>
       <c r="J3" t="n">
         <v>165</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6696428542918696</v>
       </c>
       <c r="J4" t="n">
         <v>95</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5149999856948853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.7766990507005224</v>
       </c>
       <c r="J5" t="n">
         <v>95</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44.375</v>
+        <v>43.63999938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2028169014084507</v>
+        <v>0.2062328168165564</v>
       </c>
       <c r="J6" t="n">
         <v>95</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.099999904632568</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.666666833181238</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>74</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.98500061035156</v>
+        <v>24.05500030517578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.12570353608193</v>
+        <v>1.122427755454676</v>
       </c>
       <c r="J8" t="n">
         <v>74</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.80999946594238</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="I9" t="n">
-        <v>2.378073408707304</v>
+        <v>2.423993411262447</v>
       </c>
       <c r="J9" t="n">
         <v>74</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.860000133514404</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I10" t="n">
-        <v>3.412969205515265</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J10" t="n">
         <v>67</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.42000007629395</v>
+        <v>10.25</v>
       </c>
       <c r="I11" t="n">
-        <v>4.414587299730683</v>
+        <v>4.487804878048781</v>
       </c>
       <c r="J11" t="n">
         <v>46</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.550000190734863</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7947019666784939</v>
+        <v>0.8053691481358354</v>
       </c>
       <c r="J12" t="n">
         <v>39</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5149999856948853</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.7766990507005224</v>
       </c>
       <c r="J13" t="n">
         <v>39</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.78000020980835</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6574394225023736</v>
+        <v>0.6397306335680673</v>
       </c>
       <c r="J15" t="n">
         <v>18</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.98500061035156</v>
+        <v>24.05500030517578</v>
       </c>
       <c r="I16" t="n">
-        <v>1.12570353608193</v>
+        <v>1.122427755454676</v>
       </c>
       <c r="J16" t="n">
         <v>11</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.952999949455261</v>
+        <v>1.937000036239624</v>
       </c>
       <c r="I17" t="n">
-        <v>2.918586865089202</v>
+        <v>2.942694833948294</v>
       </c>
       <c r="J17" t="n">
         <v>11</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>44.375</v>
+        <v>43.63999938964844</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2028169014084507</v>
+        <v>0.2062328168165564</v>
       </c>
       <c r="J18" t="n">
         <v>11</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.15000152587891</v>
+        <v>97.25</v>
       </c>
       <c r="I19" t="n">
-        <v>1.412639382309967</v>
+        <v>1.367609254498715</v>
       </c>
       <c r="J19" t="n">
         <v>11</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.400000095367432</v>
+        <v>6.420000076293945</v>
       </c>
       <c r="I20" t="n">
-        <v>4.687499930150808</v>
+        <v>4.672897140729944</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.5149999856948853</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.7766990507005224</v>
       </c>
       <c r="J21" t="n">
         <v>-17</v>
@@ -1547,7 +1547,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1904,7 +1904,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2033,14 +2033,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2050,14 +2050,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2067,14 +2067,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2244,7 +2244,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2271,14 +2271,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2288,14 +2288,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2305,14 +2305,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2329,7 +2329,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2373,14 +2373,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2390,14 +2390,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2407,14 +2407,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2424,14 +2424,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2567,7 +2567,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2584,7 +2584,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2618,7 +2618,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2652,7 +2652,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2713,14 +2713,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2737,7 +2737,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ENTERA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2788,7 +2788,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENTERA</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2815,14 +2815,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2832,14 +2832,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2849,14 +2849,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3206,14 +3206,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3240,14 +3240,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3281,7 +3281,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3315,7 +3315,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3332,7 +3332,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3400,7 +3400,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3427,14 +3427,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3444,14 +3444,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3519,7 +3519,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3529,14 +3529,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3546,14 +3546,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3570,7 +3570,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3614,14 +3614,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3648,14 +3648,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3665,14 +3665,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3689,7 +3689,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3723,7 +3723,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3750,14 +3750,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3791,7 +3791,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3842,7 +3842,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3876,7 +3876,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3893,7 +3893,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3920,14 +3920,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3937,14 +3937,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3978,7 +3978,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3995,7 +3995,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4029,7 +4029,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4080,7 +4080,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4097,7 +4097,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4148,7 +4148,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4165,7 +4165,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4216,7 +4216,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4335,7 +4335,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4420,7 +4420,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4505,7 +4505,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4556,7 +4556,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4583,14 +4583,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4709,7 +4709,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4760,7 +4760,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4879,7 +4879,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4964,7 +4964,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5032,7 +5032,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5212,14 +5212,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5236,7 +5236,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5270,7 +5270,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5304,7 +5304,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5355,7 +5355,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5372,7 +5372,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5382,14 +5382,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5406,7 +5406,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5457,7 +5457,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5593,7 +5593,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5610,7 +5610,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5644,7 +5644,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5661,7 +5661,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5678,7 +5678,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5712,7 +5712,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5763,7 +5763,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5780,7 +5780,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5814,7 +5814,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5831,7 +5831,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5841,14 +5841,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5865,7 +5865,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5882,7 +5882,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5899,7 +5899,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5933,7 +5933,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5950,7 +5950,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -5984,7 +5984,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -5994,14 +5994,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6018,7 +6018,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6052,7 +6052,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6069,7 +6069,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6103,7 +6103,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6120,7 +6120,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6154,7 +6154,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6188,7 +6188,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6205,7 +6205,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6222,7 +6222,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6239,7 +6239,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6273,7 +6273,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6307,7 +6307,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6402,14 +6402,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6419,14 +6419,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6436,14 +6436,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6453,14 +6453,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6470,14 +6470,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6487,14 +6487,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6504,14 +6504,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -6549,78 +6549,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>